--- a/Detroit_Pistons_2025-26_stats.xlsx
+++ b/Detroit_Pistons_2025-26_stats.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1426,6 +1426,66 @@
       </c>
       <c r="R16" t="n">
         <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>9</v>
+      </c>
+      <c r="G17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>19</v>
+      </c>
+      <c r="N17" t="n">
+        <v>14</v>
+      </c>
+      <c r="O17" t="n">
+        <v>21</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1439,7 +1499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2432,6 +2492,66 @@
       </c>
       <c r="R16" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -2445,7 +2565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3438,6 +3558,66 @@
       </c>
       <c r="R16" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>4</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3451,7 +3631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4444,6 +4624,66 @@
       </c>
       <c r="R16" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -4519,7 +4759,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.33333333333333</v>
+        <v>12.53846153846154</v>
       </c>
     </row>
     <row r="7">
@@ -4529,17 +4769,17 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10.66666666666667</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ronald Holland II</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="9">
@@ -4549,47 +4789,47 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>9.555555555555555</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tolu Smith</t>
+          <t>Ronald Holland II</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8.5</v>
+        <v>9.23076923076923</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Tolu Smith</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8.428571428571429</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Javonte Green</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.8</v>
+        <v>7.153846153846154</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Javonte Green</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7.090909090909091</v>
       </c>
     </row>
     <row r="14">
@@ -4599,13 +4839,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.125</v>
+        <v>3.444444444444445</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bobi Klintman</t>
+          <t>Wendell Moore Jr.</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -4615,11 +4855,11 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Wendell Moore Jr.</t>
+          <t>Bobi Klintman</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -4671,41 +4911,41 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.4</v>
+        <v>3.625</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Caris LeVert</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Caris LeVert</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.625</v>
+        <v>2.833333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -4715,7 +4955,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.833333333333333</v>
+        <v>1.846153846153846</v>
       </c>
     </row>
     <row r="8">
@@ -4725,7 +4965,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.666666666666667</v>
+        <v>1.769230769230769</v>
       </c>
     </row>
     <row r="9">
@@ -4741,47 +4981,47 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Isaiah Stewart</t>
+          <t>Wendell Moore Jr.</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.555555555555556</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Javonte Green</t>
+          <t>Isaiah Stewart</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.166666666666667</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Javonte Green</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>1.307692307692308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Wendell Moore Jr.</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>1.181818181818182</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Tolu Smith</t>
+          <t>Chaz Lanier</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -4791,21 +5031,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bobi Klintman</t>
+          <t>Tolu Smith</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Chaz Lanier</t>
+          <t>Bobi Klintman</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="17">
@@ -4861,7 +5101,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.666666666666667</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4">
@@ -4911,7 +5151,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.5</v>
+        <v>4.818181818181818</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +5161,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.75</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="10">
@@ -4931,27 +5171,27 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.416666666666667</v>
+        <v>3.846153846153846</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bobi Klintman</t>
+          <t>Duncan Robinson</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.2</v>
+        <v>2.846153846153846</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Duncan Robinson</t>
+          <t>Bobi Klintman</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.583333333333333</v>
+        <v>2.666666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -4961,7 +5201,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.857142857142857</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -4971,7 +5211,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.25</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="15">
@@ -4981,27 +5221,27 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.75</v>
+        <v>1.111111111111111</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Isaac Jones</t>
+          <t>Wendell Moore Jr.</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Wendell Moore Jr.</t>
+          <t>Isaac Jones</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -5053,51 +5293,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tobias Harris</t>
+          <t>Daniss Jenkins</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.333333333333333</v>
+        <v>1.375</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Isaiah Stewart</t>
+          <t>Caris LeVert</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.222222222222222</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Caris LeVert</t>
+          <t>Tobias Harris</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.125</v>
+        <v>1.333333333333333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ronald Holland II</t>
+          <t>Isaiah Stewart</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.083333333333333</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daniss Jenkins</t>
+          <t>Ronald Holland II</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -5107,7 +5347,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8333333333333334</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -5117,7 +5357,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.75</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="11">
@@ -5127,13 +5367,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Paul Reed</t>
+          <t>Ausar Thompson</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -5143,11 +5383,11 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ausar Thompson</t>
+          <t>Paul Reed</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="14">
@@ -5201,7 +5441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5483,6 +5723,27 @@
         <v>237</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PHI</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>114</v>
+      </c>
+      <c r="D14" t="n">
+        <v>105</v>
+      </c>
+      <c r="E14" t="n">
+        <v>219</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
